--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyDiagnosticReportBacteriology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA MICROBIOLOGY (file 63.05) to FHIR DiagnosticReport</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Purpose</t>
